--- a/precios_mayoristas_PRO_x12.xlsx
+++ b/precios_mayoristas_PRO_x12.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A A CATÁLOGOS\1A CATÁLOGO MAYORISTA FINAL 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86AA161-1098-4D3B-87D0-A93AA1A05524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BC04CE-F802-4DDE-9E38-B9FA61603A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="506">
   <si>
     <t>Nombre del producto</t>
   </si>
@@ -2872,6 +2872,24 @@
   </si>
   <si>
     <t>TEATROS CON TÍTERES</t>
+  </si>
+  <si>
+    <t>Mini teatro Fondo del Mar con Títeres de dedo de Animalitos marinos</t>
+  </si>
+  <si>
+    <t>Mis amigos del Celeste Océano</t>
+  </si>
+  <si>
+    <t>Títeres de dedo de Animalitos del Mar</t>
+  </si>
+  <si>
+    <t>el Gato y los cinco Ratoncitos Bailarines</t>
+  </si>
+  <si>
+    <t>Teatro Fondo del mar con Títeres del Océano</t>
+  </si>
+  <si>
+    <t>Pack x 10 Títeres de mano de Animalitos- Surtido a elección</t>
   </si>
 </sst>
 </file>
@@ -3251,12 +3269,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W200"/>
+  <dimension ref="A1:W206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74.42578125" customWidth="1"/>
-    <col min="2" max="3" width="31.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" customWidth="1"/>
+    <col min="3" max="4" width="13.5703125" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" customWidth="1"/>
     <col min="20" max="21" width="34.42578125" customWidth="1"/>
     <col min="22" max="22" width="55.42578125" style="2" customWidth="1"/>
@@ -3333,7 +3351,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3356,7 +3374,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3379,7 +3397,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -3402,7 +3420,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -3425,7 +3443,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3448,7 +3466,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -3471,7 +3489,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -3494,7 +3512,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3517,7 +3535,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -3540,7 +3558,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -3563,7 +3581,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -3586,7 +3604,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -3609,7 +3627,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -3632,7 +3650,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3655,7 +3673,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -3678,7 +3696,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -3701,7 +3719,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -3724,7 +3742,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -3747,7 +3765,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -3770,7 +3788,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -3793,7 +3811,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -3816,7 +3834,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -3839,7 +3857,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -3862,7 +3880,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="300" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -3885,7 +3903,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3908,7 +3926,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -3931,7 +3949,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -3954,7 +3972,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3977,7 +3995,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -4000,7 +4018,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>202</v>
       </c>
@@ -4023,7 +4041,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -4046,7 +4064,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -4069,7 +4087,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="210" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -4092,7 +4110,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="210" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -4115,7 +4133,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -4138,7 +4156,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="180" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -4161,7 +4179,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -4184,7 +4202,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -4207,7 +4225,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="165" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -4230,7 +4248,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -4253,7 +4271,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>54</v>
       </c>
@@ -4276,7 +4294,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>55</v>
       </c>
@@ -4299,7 +4317,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -4322,7 +4340,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -4345,7 +4363,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>58</v>
       </c>
@@ -4368,7 +4386,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>359</v>
       </c>
@@ -4391,7 +4409,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -4414,7 +4432,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -4437,7 +4455,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -4460,7 +4478,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -4483,7 +4501,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -4506,7 +4524,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -4529,7 +4547,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -4552,7 +4570,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>491</v>
       </c>
@@ -4575,7 +4593,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -4598,7 +4616,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>67</v>
       </c>
@@ -4621,7 +4639,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -4644,7 +4662,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -4667,7 +4685,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -4690,7 +4708,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>71</v>
       </c>
@@ -4713,7 +4731,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>72</v>
       </c>
@@ -4736,7 +4754,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>73</v>
       </c>
@@ -4759,7 +4777,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -4782,7 +4800,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -4805,7 +4823,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -4831,7 +4849,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="210" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>472</v>
       </c>
@@ -4851,7 +4869,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="210" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>473</v>
       </c>
@@ -4871,7 +4889,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="69" spans="1:23" ht="210" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>474</v>
       </c>
@@ -4891,7 +4909,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="210" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>471</v>
       </c>
@@ -4914,7 +4932,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="360" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>209</v>
       </c>
@@ -4955,7 +4973,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>210</v>
       </c>
@@ -4990,7 +5008,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>211</v>
       </c>
@@ -5013,7 +5031,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>212</v>
       </c>
@@ -5036,7 +5054,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>213</v>
       </c>
@@ -5059,7 +5077,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>214</v>
       </c>
@@ -5082,7 +5100,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>215</v>
       </c>
@@ -5114,7 +5132,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>216</v>
       </c>
@@ -5137,7 +5155,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>217</v>
       </c>
@@ -5160,7 +5178,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>218</v>
       </c>
@@ -5183,7 +5201,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>219</v>
       </c>
@@ -5206,7 +5224,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>229</v>
       </c>
@@ -5229,7 +5247,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>220</v>
       </c>
@@ -5252,7 +5270,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>221</v>
       </c>
@@ -5275,7 +5293,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>222</v>
       </c>
@@ -5307,7 +5325,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>77</v>
       </c>
@@ -5339,7 +5357,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>78</v>
       </c>
@@ -5368,122 +5386,128 @@
         <v>177</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>79</v>
+        <v>500</v>
       </c>
       <c r="B88" t="s">
-        <v>437</v>
+        <v>195</v>
       </c>
       <c r="C88">
         <v>18</v>
       </c>
-      <c r="D88">
-        <v>19500</v>
-      </c>
-      <c r="F88" t="s">
-        <v>168</v>
-      </c>
-      <c r="U88" t="s">
-        <v>454</v>
-      </c>
-      <c r="V88" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="W88" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="89" spans="1:23" ht="225" x14ac:dyDescent="0.25">
+      <c r="I88">
+        <v>16300</v>
+      </c>
+      <c r="J88">
+        <v>18150</v>
+      </c>
+      <c r="K88">
+        <v>19920</v>
+      </c>
+      <c r="L88">
+        <v>21800</v>
+      </c>
+      <c r="M88">
+        <v>23550</v>
+      </c>
+      <c r="N88">
+        <v>25350</v>
+      </c>
+      <c r="O88">
+        <v>27200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
         <v>437</v>
       </c>
       <c r="C89">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D89">
-        <v>23200</v>
+        <v>19500</v>
       </c>
       <c r="F89" t="s">
         <v>168</v>
       </c>
       <c r="U89" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="W89" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B90" t="s">
         <v>437</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D90">
-        <v>19850</v>
+        <v>23200</v>
       </c>
       <c r="F90" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U90" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="W90" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
         <v>437</v>
       </c>
       <c r="C91">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D91">
-        <v>33300</v>
+        <v>19850</v>
       </c>
       <c r="F91" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U91" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="V91" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="W91" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B92" t="s">
         <v>437</v>
       </c>
       <c r="C92">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D92">
-        <v>23970</v>
+        <v>33300</v>
       </c>
       <c r="F92" t="s">
         <v>168</v>
@@ -5492,21 +5516,21 @@
         <v>451</v>
       </c>
       <c r="V92" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="W92" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="93" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B93" t="s">
         <v>437</v>
       </c>
       <c r="C93">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D93">
         <v>23970</v>
@@ -5518,21 +5542,21 @@
         <v>451</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="W93" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B94" t="s">
         <v>437</v>
       </c>
       <c r="C94">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D94">
         <v>23970</v>
@@ -5544,24 +5568,24 @@
         <v>451</v>
       </c>
       <c r="V94" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="W94" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
         <v>437</v>
       </c>
       <c r="C95">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D95">
-        <v>24850</v>
+        <v>23970</v>
       </c>
       <c r="F95" t="s">
         <v>168</v>
@@ -5570,21 +5594,21 @@
         <v>451</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="W95" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B96" t="s">
         <v>437</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D96">
         <v>24850</v>
@@ -5596,21 +5620,21 @@
         <v>451</v>
       </c>
       <c r="V96" s="2" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="W96" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B97" t="s">
         <v>437</v>
       </c>
       <c r="C97">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D97">
         <v>24850</v>
@@ -5622,24 +5646,24 @@
         <v>451</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="W97" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B98" t="s">
         <v>437</v>
       </c>
       <c r="C98">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D98">
-        <v>27400</v>
+        <v>24850</v>
       </c>
       <c r="F98" t="s">
         <v>168</v>
@@ -5648,293 +5672,296 @@
         <v>451</v>
       </c>
       <c r="V98" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="W98" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B99" t="s">
         <v>437</v>
       </c>
       <c r="C99">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D99">
-        <v>22500</v>
+        <v>27400</v>
       </c>
       <c r="F99" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U99" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="W99" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="270" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B100" t="s">
         <v>437</v>
       </c>
       <c r="C100">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D100">
-        <v>24500</v>
+        <v>22500</v>
       </c>
       <c r="F100" t="s">
         <v>169</v>
       </c>
       <c r="U100" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="W100" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B101" t="s">
         <v>437</v>
       </c>
       <c r="C101">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D101">
-        <v>38500</v>
+        <v>24500</v>
       </c>
       <c r="F101" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U101" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>440</v>
+        <v>395</v>
       </c>
       <c r="W101" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B102" t="s">
         <v>437</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D102">
-        <v>28500</v>
+        <v>38500</v>
       </c>
       <c r="F102" t="s">
         <v>170</v>
       </c>
       <c r="U102" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="W102" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>436</v>
+        <v>93</v>
       </c>
       <c r="B103" t="s">
         <v>437</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D103">
-        <v>45000</v>
+        <v>28500</v>
       </c>
       <c r="F103" t="s">
         <v>170</v>
       </c>
-      <c r="T103" t="s">
-        <v>441</v>
-      </c>
       <c r="U103" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="V103" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="W103" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>94</v>
+        <v>436</v>
       </c>
       <c r="B104" t="s">
         <v>437</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D104">
-        <v>53200</v>
+        <v>45000</v>
       </c>
       <c r="F104" t="s">
         <v>170</v>
       </c>
+      <c r="T104" t="s">
+        <v>441</v>
+      </c>
       <c r="U104" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>389</v>
+        <v>438</v>
       </c>
       <c r="W104" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B105" t="s">
         <v>437</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>51800</v>
+        <v>53200</v>
       </c>
       <c r="F105" t="s">
         <v>170</v>
       </c>
       <c r="U105" t="s">
+        <v>447</v>
+      </c>
+      <c r="V105" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="W105" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>95</v>
+      </c>
+      <c r="B106" t="s">
+        <v>437</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
+      </c>
+      <c r="D106">
+        <v>51800</v>
+      </c>
+      <c r="F106" t="s">
+        <v>170</v>
+      </c>
+      <c r="U106" t="s">
         <v>448</v>
       </c>
-      <c r="V105" s="2" t="s">
+      <c r="V106" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="W105" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="106" spans="1:23" ht="255" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="W106" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>96</v>
-      </c>
-      <c r="B106" t="s">
-        <v>399</v>
-      </c>
-      <c r="C106">
-        <v>5</v>
-      </c>
-      <c r="D106">
-        <v>25300</v>
-      </c>
-      <c r="F106" t="s">
-        <v>168</v>
-      </c>
-      <c r="T106" t="s">
-        <v>404</v>
-      </c>
-      <c r="U106" t="s">
-        <v>449</v>
-      </c>
-      <c r="V106" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="W106" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="107" spans="1:23" ht="240" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>97</v>
       </c>
       <c r="B107" t="s">
         <v>399</v>
       </c>
       <c r="C107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107">
-        <v>32000</v>
+        <v>25300</v>
       </c>
       <c r="F107" t="s">
         <v>168</v>
       </c>
       <c r="T107" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="U107" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="W107" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="108" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>403</v>
+        <v>97</v>
       </c>
       <c r="B108" t="s">
         <v>399</v>
       </c>
       <c r="C108">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D108">
-        <v>25500</v>
+        <v>32000</v>
+      </c>
+      <c r="F108" t="s">
+        <v>168</v>
       </c>
       <c r="T108" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="U108" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="V108" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="109" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+      <c r="W108" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B109" t="s">
         <v>399</v>
       </c>
       <c r="C109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D109">
         <v>25500</v>
       </c>
       <c r="T109" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="U109" t="s">
         <v>449</v>
@@ -5943,21 +5970,21 @@
         <v>381</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B110" t="s">
         <v>399</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D110">
         <v>25500</v>
       </c>
       <c r="T110" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="U110" t="s">
         <v>449</v>
@@ -5966,24 +5993,21 @@
         <v>381</v>
       </c>
     </row>
-    <row r="111" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B111" t="s">
         <v>399</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>25500</v>
       </c>
-      <c r="F111" t="s">
-        <v>168</v>
-      </c>
       <c r="T111" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="U111" t="s">
         <v>449</v>
@@ -5991,71 +6015,71 @@
       <c r="V111" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="W111" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="112" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>103</v>
+        <v>400</v>
       </c>
       <c r="B112" t="s">
         <v>399</v>
       </c>
       <c r="C112">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D112">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="F112" t="s">
         <v>168</v>
       </c>
       <c r="T112" t="s">
-        <v>410</v>
+        <v>409</v>
+      </c>
+      <c r="U112" t="s">
+        <v>449</v>
       </c>
       <c r="V112" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="W112" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="113" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
         <v>399</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D113">
-        <v>23500</v>
+        <v>25000</v>
       </c>
       <c r="F113" t="s">
         <v>168</v>
       </c>
       <c r="T113" t="s">
-        <v>290</v>
+        <v>410</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="W113" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="114" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B114" t="s">
         <v>399</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D114">
         <v>23500</v>
@@ -6064,64 +6088,67 @@
         <v>168</v>
       </c>
       <c r="T114" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="W114" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="115" spans="1:23" ht="180" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B115" t="s">
         <v>399</v>
       </c>
       <c r="C115">
+        <v>8</v>
+      </c>
+      <c r="D115">
+        <v>23500</v>
+      </c>
+      <c r="F115" t="s">
+        <v>168</v>
+      </c>
+      <c r="T115" t="s">
+        <v>291</v>
+      </c>
+      <c r="V115" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="W115" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>105</v>
+      </c>
+      <c r="B116" t="s">
+        <v>399</v>
+      </c>
+      <c r="C116">
         <v>10</v>
       </c>
-      <c r="D115">
+      <c r="D116">
         <v>9000</v>
       </c>
-      <c r="T115" t="s">
+      <c r="T116" t="s">
         <v>411</v>
       </c>
-      <c r="V115" s="2" t="s">
+      <c r="V116" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="W115" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="116" spans="1:23" ht="285" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="W116" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>98</v>
-      </c>
-      <c r="B116" t="s">
-        <v>496</v>
-      </c>
-      <c r="D116">
-        <v>18000</v>
-      </c>
-      <c r="F116" t="s">
-        <v>168</v>
-      </c>
-      <c r="T116" t="s">
-        <v>280</v>
-      </c>
-      <c r="V116" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="W116" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="117" spans="1:23" ht="285" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>99</v>
       </c>
       <c r="B117" t="s">
         <v>496</v>
@@ -6133,7 +6160,7 @@
         <v>168</v>
       </c>
       <c r="T117" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="V117" s="2" t="s">
         <v>297</v>
@@ -6142,55 +6169,55 @@
         <v>177</v>
       </c>
     </row>
-    <row r="118" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B118" t="s">
         <v>496</v>
       </c>
       <c r="D118">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="F118" t="s">
         <v>168</v>
       </c>
       <c r="T118" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>377</v>
+        <v>297</v>
       </c>
       <c r="W118" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B119" t="s">
         <v>496</v>
       </c>
       <c r="D119">
-        <v>23500</v>
+        <v>22000</v>
       </c>
       <c r="F119" t="s">
         <v>168</v>
       </c>
       <c r="T119" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="W119" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B120" t="s">
         <v>496</v>
@@ -6202,64 +6229,64 @@
         <v>168</v>
       </c>
       <c r="T120" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="W120" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B121" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D121">
-        <v>25200</v>
+        <v>23500</v>
       </c>
       <c r="F121" t="s">
         <v>168</v>
       </c>
       <c r="T121" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="W121" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="122" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B122" t="s">
         <v>497</v>
       </c>
       <c r="D122">
-        <v>23500</v>
+        <v>25200</v>
       </c>
       <c r="F122" t="s">
         <v>168</v>
       </c>
       <c r="T122" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>297</v>
+        <v>434</v>
       </c>
       <c r="W122" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B123" t="s">
         <v>497</v>
@@ -6271,7 +6298,7 @@
         <v>168</v>
       </c>
       <c r="T123" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="V123" s="2" t="s">
         <v>297</v>
@@ -6280,9 +6307,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="124" spans="1:23" ht="285" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B124" t="s">
         <v>497</v>
@@ -6294,38 +6321,41 @@
         <v>168</v>
       </c>
       <c r="T124" t="s">
+        <v>286</v>
+      </c>
+      <c r="V124" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="W124" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>109</v>
+      </c>
+      <c r="B125" t="s">
+        <v>497</v>
+      </c>
+      <c r="D125">
+        <v>23500</v>
+      </c>
+      <c r="F125" t="s">
+        <v>168</v>
+      </c>
+      <c r="T125" t="s">
         <v>291</v>
       </c>
-      <c r="V124" s="2" t="s">
+      <c r="V125" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="W124" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="125" spans="1:23" ht="270" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="W125" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>110</v>
-      </c>
-      <c r="B125" t="s">
-        <v>496</v>
-      </c>
-      <c r="D125">
-        <v>15000</v>
-      </c>
-      <c r="T125" t="s">
-        <v>288</v>
-      </c>
-      <c r="V125" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="W125" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="126" spans="1:23" ht="270" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>111</v>
       </c>
       <c r="B126" t="s">
         <v>496</v>
@@ -6334,7 +6364,7 @@
         <v>15000</v>
       </c>
       <c r="T126" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V126" s="2" t="s">
         <v>414</v>
@@ -6343,1086 +6373,1296 @@
         <v>177</v>
       </c>
     </row>
-    <row r="127" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B127" t="s">
-        <v>498</v>
-      </c>
-      <c r="C127">
-        <v>1</v>
+        <v>496</v>
       </c>
       <c r="D127">
-        <v>23200</v>
+        <v>15000</v>
+      </c>
+      <c r="T127" t="s">
+        <v>289</v>
       </c>
       <c r="V127" s="2" t="s">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="W127" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>113</v>
+        <v>501</v>
       </c>
       <c r="B128" t="s">
         <v>498</v>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="G128">
+        <v>4000</v>
+      </c>
+      <c r="H128">
+        <v>7612</v>
+      </c>
+      <c r="I128">
+        <v>11450</v>
       </c>
       <c r="J128">
-        <v>11850</v>
+        <v>15250</v>
       </c>
       <c r="K128">
-        <v>16500</v>
+        <v>19100</v>
       </c>
       <c r="L128">
-        <v>19700</v>
+        <v>22850</v>
       </c>
       <c r="M128">
-        <v>22860</v>
+        <v>26650</v>
       </c>
       <c r="N128">
-        <v>26100</v>
+        <v>30950</v>
       </c>
       <c r="O128">
-        <v>29300</v>
+        <v>34260</v>
       </c>
       <c r="P128">
-        <v>33200</v>
+        <v>38100</v>
       </c>
       <c r="Q128">
-        <v>35700</v>
+        <v>41865</v>
       </c>
       <c r="R128">
-        <v>38800</v>
-      </c>
-      <c r="V128" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="W128" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="129" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+        <v>45700</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B129" t="s">
         <v>498</v>
       </c>
       <c r="C129">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>4000</v>
+      </c>
+      <c r="H129">
+        <v>7612</v>
+      </c>
+      <c r="I129">
+        <v>11450</v>
+      </c>
+      <c r="J129">
+        <v>15250</v>
       </c>
       <c r="K129">
-        <v>16500</v>
-      </c>
-      <c r="M129">
-        <v>26350</v>
+        <v>19100</v>
+      </c>
+      <c r="L129">
+        <v>22850</v>
       </c>
       <c r="V129" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="W129" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="130" spans="1:23" ht="360" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B130" t="s">
         <v>498</v>
       </c>
       <c r="C130">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="G130">
+        <v>4000</v>
+      </c>
+      <c r="H130">
+        <v>7612</v>
+      </c>
+      <c r="I130">
+        <v>11450</v>
       </c>
       <c r="J130">
-        <v>11850</v>
+        <v>15250</v>
       </c>
       <c r="K130">
-        <v>16500</v>
+        <v>19100</v>
       </c>
       <c r="L130">
-        <v>19700</v>
+        <v>22850</v>
       </c>
       <c r="M130">
-        <v>22860</v>
+        <v>26650</v>
       </c>
       <c r="N130">
-        <v>26100</v>
+        <v>30950</v>
+      </c>
+      <c r="O130">
+        <v>34260</v>
       </c>
       <c r="V130" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="W130" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="131" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>116</v>
+        <v>503</v>
       </c>
       <c r="B131" t="s">
         <v>498</v>
       </c>
       <c r="C131">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D131">
-        <v>19000</v>
-      </c>
-      <c r="V131" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="W131" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="132" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B132" t="s">
         <v>498</v>
       </c>
       <c r="C132">
-        <v>9</v>
-      </c>
-      <c r="D132">
-        <v>20300</v>
+        <v>10</v>
+      </c>
+      <c r="K132">
+        <v>19100</v>
+      </c>
+      <c r="L132">
+        <v>24575</v>
+      </c>
+      <c r="M132">
+        <v>30120</v>
       </c>
       <c r="V132" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="W132" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="133" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B133" t="s">
         <v>498</v>
       </c>
       <c r="C133">
-        <v>3</v>
-      </c>
-      <c r="D133">
-        <v>20300</v>
+        <v>5</v>
+      </c>
+      <c r="G133">
+        <v>4000</v>
+      </c>
+      <c r="H133">
+        <v>7612</v>
+      </c>
+      <c r="I133">
+        <v>11450</v>
+      </c>
+      <c r="J133">
+        <v>15250</v>
+      </c>
+      <c r="K133">
+        <v>19100</v>
+      </c>
+      <c r="L133">
+        <v>22850</v>
+      </c>
+      <c r="M133">
+        <v>26650</v>
+      </c>
+      <c r="N133">
+        <v>30950</v>
       </c>
       <c r="V133" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="W133" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="134" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B134" t="s">
         <v>498</v>
       </c>
       <c r="C134">
-        <v>6</v>
-      </c>
-      <c r="D134">
-        <v>25200</v>
+        <v>8</v>
+      </c>
+      <c r="G134">
+        <v>4000</v>
+      </c>
+      <c r="H134">
+        <v>7612</v>
+      </c>
+      <c r="I134">
+        <v>11450</v>
+      </c>
+      <c r="J134">
+        <v>15250</v>
+      </c>
+      <c r="K134">
+        <v>19100</v>
+      </c>
+      <c r="L134">
+        <v>22850</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="W134" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="135" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B135" t="s">
         <v>498</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D135">
-        <v>20300</v>
+        <v>22200</v>
       </c>
       <c r="V135" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="W135" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="136" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B136" t="s">
         <v>498</v>
       </c>
       <c r="C136">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D136">
-        <v>20300</v>
+        <v>22200</v>
       </c>
       <c r="V136" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="W136" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="137" spans="1:23" ht="345" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B137" t="s">
         <v>498</v>
       </c>
       <c r="C137">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D137">
-        <v>11850</v>
+        <v>24300</v>
       </c>
       <c r="V137" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="W137" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="138" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B138" t="s">
         <v>498</v>
       </c>
       <c r="C138">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D138">
-        <v>20300</v>
+        <v>22200</v>
       </c>
       <c r="V138" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="W138" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="139" spans="1:23" ht="360" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B139" t="s">
         <v>498</v>
       </c>
       <c r="C139">
-        <v>13</v>
-      </c>
-      <c r="I139">
-        <v>15400</v>
-      </c>
-      <c r="J139">
-        <v>20300</v>
-      </c>
-      <c r="K139">
-        <v>25200</v>
-      </c>
-      <c r="L139">
-        <v>30200</v>
-      </c>
-      <c r="M139">
-        <v>35100</v>
+        <v>11</v>
+      </c>
+      <c r="D139">
+        <v>22200</v>
       </c>
       <c r="V139" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="W139" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="140" spans="1:23" ht="345" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B140" t="s">
         <v>498</v>
       </c>
       <c r="C140">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D140">
-        <v>29450</v>
+        <v>15250</v>
       </c>
       <c r="V140" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="W140" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="141" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B141" t="s">
         <v>498</v>
       </c>
       <c r="C141">
-        <v>14</v>
-      </c>
-      <c r="J141">
-        <v>20300</v>
-      </c>
-      <c r="K141">
-        <v>25200</v>
-      </c>
-      <c r="L141">
-        <v>30200</v>
-      </c>
-      <c r="M141">
-        <v>35100</v>
-      </c>
-      <c r="N141">
-        <v>39960</v>
-      </c>
-      <c r="O141">
-        <v>44900</v>
-      </c>
-      <c r="P141">
-        <v>54750</v>
+        <v>4</v>
+      </c>
+      <c r="D141">
+        <v>22200</v>
       </c>
       <c r="V141" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="W141" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="142" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B142" t="s">
         <v>498</v>
       </c>
       <c r="C142">
-        <v>15</v>
-      </c>
-      <c r="D142">
-        <v>20300</v>
+        <v>13</v>
+      </c>
+      <c r="G142">
+        <v>5700</v>
+      </c>
+      <c r="H142">
+        <v>11050</v>
+      </c>
+      <c r="I142">
+        <v>16650</v>
+      </c>
+      <c r="J142">
+        <v>22200</v>
+      </c>
+      <c r="K142">
+        <v>27800</v>
+      </c>
+      <c r="L142">
+        <v>33300</v>
+      </c>
+      <c r="M142">
+        <v>38820</v>
       </c>
       <c r="V142" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="W142" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="143" spans="1:23" ht="405" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B143" t="s">
         <v>498</v>
       </c>
       <c r="C143">
-        <v>17</v>
-      </c>
-      <c r="J143">
-        <v>11850</v>
-      </c>
-      <c r="K143">
-        <v>16500</v>
-      </c>
-      <c r="L143">
-        <v>19700</v>
-      </c>
-      <c r="M143">
-        <v>22860</v>
-      </c>
-      <c r="N143">
-        <v>26100</v>
-      </c>
-      <c r="O143">
-        <v>29300</v>
-      </c>
-      <c r="P143">
-        <v>33200</v>
-      </c>
-      <c r="Q143">
-        <v>35700</v>
-      </c>
-      <c r="R143">
-        <v>38800</v>
+        <v>16</v>
       </c>
       <c r="V143" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="W143" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="144" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B144" t="s">
         <v>498</v>
       </c>
       <c r="C144">
-        <v>18</v>
-      </c>
-      <c r="D144">
-        <v>11200</v>
+        <v>14</v>
+      </c>
+      <c r="G144">
+        <v>5700</v>
+      </c>
+      <c r="H144">
+        <v>11050</v>
+      </c>
+      <c r="I144">
+        <v>16650</v>
+      </c>
+      <c r="J144">
+        <v>22200</v>
+      </c>
+      <c r="K144">
+        <v>27800</v>
+      </c>
+      <c r="L144">
+        <v>33300</v>
+      </c>
+      <c r="M144">
+        <v>38820</v>
+      </c>
+      <c r="N144">
+        <v>39960</v>
+      </c>
+      <c r="O144">
+        <v>44900</v>
+      </c>
+      <c r="P144">
+        <v>54750</v>
       </c>
       <c r="V144" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="W144" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="145" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B145" t="s">
         <v>498</v>
       </c>
       <c r="C145">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D145">
-        <v>41200</v>
+        <v>22200</v>
       </c>
       <c r="V145" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="W145" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="146" spans="1:23" ht="345" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B146" t="s">
         <v>498</v>
       </c>
       <c r="C146">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="G146">
+        <v>4000</v>
+      </c>
+      <c r="H146">
+        <v>7612</v>
       </c>
       <c r="I146">
-        <v>11200</v>
+        <v>11450</v>
+      </c>
+      <c r="J146">
+        <v>15250</v>
       </c>
       <c r="K146">
-        <v>19960</v>
+        <v>19100</v>
+      </c>
+      <c r="L146">
+        <v>22850</v>
+      </c>
+      <c r="M146">
+        <v>26650</v>
+      </c>
+      <c r="N146">
+        <v>30950</v>
+      </c>
+      <c r="O146">
+        <v>34260</v>
+      </c>
+      <c r="P146">
+        <v>38100</v>
+      </c>
+      <c r="Q146">
+        <v>41865</v>
+      </c>
+      <c r="R146">
+        <v>45700</v>
       </c>
       <c r="V146" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="W146" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="147" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B147" t="s">
         <v>498</v>
       </c>
       <c r="C147">
-        <v>21</v>
-      </c>
-      <c r="D147">
-        <v>30200</v>
+        <v>18</v>
       </c>
       <c r="V147" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="W147" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="148" spans="1:23" ht="330" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B148" t="s">
         <v>498</v>
       </c>
       <c r="C148">
+        <v>19</v>
+      </c>
+      <c r="G148">
+        <v>5700</v>
+      </c>
+      <c r="H148">
+        <v>11050</v>
+      </c>
+      <c r="I148">
+        <v>16650</v>
+      </c>
+      <c r="J148">
+        <v>22200</v>
+      </c>
+      <c r="K148">
+        <v>27800</v>
+      </c>
+      <c r="L148">
+        <v>33300</v>
+      </c>
+      <c r="M148">
+        <v>38820</v>
+      </c>
+      <c r="N148">
+        <v>39960</v>
+      </c>
+      <c r="O148">
+        <v>44900</v>
+      </c>
+      <c r="P148">
+        <v>54750</v>
+      </c>
+      <c r="V148" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="W148" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>131</v>
+      </c>
+      <c r="B149" t="s">
+        <v>498</v>
+      </c>
+      <c r="C149">
+        <v>20</v>
+      </c>
+      <c r="G149">
+        <v>4000</v>
+      </c>
+      <c r="H149">
+        <v>7612</v>
+      </c>
+      <c r="I149">
+        <v>11450</v>
+      </c>
+      <c r="J149">
+        <v>16970</v>
+      </c>
+      <c r="K149">
+        <v>22508</v>
+      </c>
+      <c r="V149" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="W149" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>132</v>
+      </c>
+      <c r="B150" t="s">
+        <v>498</v>
+      </c>
+      <c r="C150">
+        <v>21</v>
+      </c>
+      <c r="V150" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="W150" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>133</v>
+      </c>
+      <c r="B151" t="s">
+        <v>498</v>
+      </c>
+      <c r="C151">
         <v>22</v>
       </c>
-      <c r="D148">
-        <v>30200</v>
-      </c>
-      <c r="V148" s="2" t="s">
+      <c r="V151" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="W148" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="149" spans="1:23" ht="390" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="W151" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>505</v>
+      </c>
+      <c r="B152" t="s">
+        <v>498</v>
+      </c>
+      <c r="C152">
+        <v>24</v>
+      </c>
+      <c r="P152">
+        <v>49760</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>134</v>
-      </c>
-      <c r="B149" t="s">
-        <v>499</v>
-      </c>
-      <c r="J149">
-        <v>29800</v>
-      </c>
-      <c r="K149">
-        <v>32980</v>
-      </c>
-      <c r="L149">
-        <v>36200</v>
-      </c>
-      <c r="M149">
-        <v>39400</v>
-      </c>
-      <c r="N149">
-        <v>46600</v>
-      </c>
-      <c r="O149">
-        <v>45800</v>
-      </c>
-      <c r="P149">
-        <v>48950</v>
-      </c>
-      <c r="Q149">
-        <v>52100</v>
-      </c>
-      <c r="R149">
-        <v>55300</v>
-      </c>
-      <c r="V149" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="W149" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="150" spans="1:23" ht="375" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>135</v>
-      </c>
-      <c r="B150" t="s">
-        <v>499</v>
-      </c>
-      <c r="J150">
-        <v>29800</v>
-      </c>
-      <c r="K150">
-        <v>32980</v>
-      </c>
-      <c r="L150">
-        <v>36200</v>
-      </c>
-      <c r="M150">
-        <v>39400</v>
-      </c>
-      <c r="N150">
-        <v>46600</v>
-      </c>
-      <c r="V150" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="W150" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="151" spans="1:23" ht="390" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>136</v>
-      </c>
-      <c r="B151" t="s">
-        <v>499</v>
-      </c>
-      <c r="D151">
-        <v>32980</v>
-      </c>
-      <c r="V151" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="W151" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="152" spans="1:23" ht="390" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>137</v>
-      </c>
-      <c r="B152" t="s">
-        <v>499</v>
-      </c>
-      <c r="D152">
-        <v>36200</v>
-      </c>
-      <c r="V152" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="W152" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="153" spans="1:23" ht="360" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>138</v>
       </c>
       <c r="B153" t="s">
         <v>499</v>
       </c>
-      <c r="D153">
-        <v>36800</v>
+      <c r="H153">
+        <v>24500</v>
+      </c>
+      <c r="I153">
+        <v>28500</v>
+      </c>
+      <c r="J153">
+        <v>30200</v>
+      </c>
+      <c r="K153">
+        <v>33400</v>
+      </c>
+      <c r="L153">
+        <v>36700</v>
+      </c>
+      <c r="M153">
+        <v>39950</v>
+      </c>
+      <c r="N153">
+        <v>43250</v>
+      </c>
+      <c r="O153">
+        <v>46500</v>
+      </c>
+      <c r="P153">
+        <v>49760</v>
+      </c>
+      <c r="Q153">
+        <v>53025</v>
+      </c>
+      <c r="R153">
+        <v>56300</v>
       </c>
       <c r="V153" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="W153" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="154" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B154" t="s">
         <v>499</v>
       </c>
-      <c r="D154">
-        <v>36800</v>
+      <c r="H154">
+        <v>24500</v>
+      </c>
+      <c r="I154">
+        <v>28500</v>
+      </c>
+      <c r="J154">
+        <v>30200</v>
+      </c>
+      <c r="K154">
+        <v>33400</v>
+      </c>
+      <c r="L154">
+        <v>36700</v>
+      </c>
+      <c r="M154">
+        <v>39950</v>
+      </c>
+      <c r="N154">
+        <v>43250</v>
       </c>
       <c r="V154" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="W154" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="155" spans="1:23" ht="360" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B155" t="s">
         <v>499</v>
       </c>
-      <c r="D155">
-        <v>38200</v>
+      <c r="H155">
+        <v>24500</v>
+      </c>
+      <c r="I155">
+        <v>28500</v>
+      </c>
+      <c r="J155">
+        <v>30200</v>
+      </c>
+      <c r="K155">
+        <v>33400</v>
+      </c>
+      <c r="L155">
+        <v>36700</v>
+      </c>
+      <c r="M155">
+        <v>39950</v>
       </c>
       <c r="V155" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="W155" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="360" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B156" t="s">
         <v>499</v>
       </c>
-      <c r="D156">
-        <v>36800</v>
+      <c r="H156">
+        <v>24500</v>
+      </c>
+      <c r="I156">
+        <v>28500</v>
+      </c>
+      <c r="J156">
+        <v>30200</v>
+      </c>
+      <c r="K156">
+        <v>33400</v>
+      </c>
+      <c r="L156">
+        <v>36700</v>
+      </c>
+      <c r="M156">
+        <v>39950</v>
       </c>
       <c r="V156" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="W156" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B157" t="s">
         <v>499</v>
       </c>
       <c r="D157">
-        <v>29800</v>
+        <v>37100</v>
       </c>
       <c r="V157" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="W157" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B158" t="s">
         <v>499</v>
       </c>
-      <c r="J158">
-        <v>36800</v>
-      </c>
-      <c r="K158">
-        <v>41700</v>
-      </c>
-      <c r="L158">
-        <v>46600</v>
-      </c>
-      <c r="M158">
-        <v>48100</v>
+      <c r="D158">
+        <v>37100</v>
       </c>
       <c r="V158" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="W158" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="159" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B159" t="s">
         <v>499</v>
       </c>
-      <c r="J159">
-        <v>29800</v>
-      </c>
-      <c r="K159">
-        <v>32980</v>
-      </c>
-      <c r="L159">
-        <v>36200</v>
-      </c>
-      <c r="M159">
-        <v>39400</v>
-      </c>
-      <c r="N159">
-        <v>46600</v>
-      </c>
-      <c r="O159">
-        <v>45800</v>
-      </c>
-      <c r="P159">
-        <v>48950</v>
-      </c>
-      <c r="Q159">
-        <v>52100</v>
-      </c>
-      <c r="R159">
-        <v>55300</v>
+      <c r="D159">
+        <v>38650</v>
       </c>
       <c r="V159" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="W159" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="360" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>145</v>
+        <v>504</v>
       </c>
       <c r="B160" t="s">
         <v>499</v>
       </c>
-      <c r="D160">
-        <v>36800</v>
-      </c>
-      <c r="V160" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="W160" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="161" spans="1:23" ht="390" x14ac:dyDescent="0.25">
+      <c r="H160">
+        <v>24500</v>
+      </c>
+      <c r="I160">
+        <v>28500</v>
+      </c>
+      <c r="J160">
+        <v>30200</v>
+      </c>
+      <c r="K160">
+        <v>33400</v>
+      </c>
+      <c r="L160">
+        <v>36700</v>
+      </c>
+      <c r="M160">
+        <v>39950</v>
+      </c>
+      <c r="N160">
+        <v>43250</v>
+      </c>
+      <c r="O160">
+        <v>46500</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B161" t="s">
         <v>499</v>
       </c>
-      <c r="J161">
-        <v>36800</v>
-      </c>
-      <c r="K161">
-        <v>41700</v>
-      </c>
-      <c r="L161">
-        <v>46600</v>
-      </c>
-      <c r="M161">
-        <v>48100</v>
+      <c r="D161">
+        <v>37100</v>
       </c>
       <c r="V161" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="W161" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B162" t="s">
         <v>499</v>
       </c>
       <c r="D162">
-        <v>36800</v>
+        <v>30200</v>
       </c>
       <c r="V162" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="W162" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="390" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B163" t="s">
         <v>499</v>
       </c>
-      <c r="D163">
-        <v>34990</v>
+      <c r="H163">
+        <v>30000</v>
+      </c>
+      <c r="I163">
+        <v>34000</v>
+      </c>
+      <c r="J163">
+        <v>37100</v>
+      </c>
+      <c r="K163">
+        <v>42100</v>
+      </c>
+      <c r="L163">
+        <v>47100</v>
+      </c>
+      <c r="M163">
+        <v>52200</v>
+      </c>
+      <c r="N163">
+        <v>57200</v>
       </c>
       <c r="V163" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="W163" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="164" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B164" t="s">
         <v>499</v>
       </c>
-      <c r="D164">
-        <v>36800</v>
+      <c r="H164">
+        <v>24500</v>
+      </c>
+      <c r="I164">
+        <v>28500</v>
+      </c>
+      <c r="J164">
+        <v>30200</v>
+      </c>
+      <c r="K164">
+        <v>33400</v>
+      </c>
+      <c r="L164">
+        <v>36700</v>
+      </c>
+      <c r="M164">
+        <v>39950</v>
+      </c>
+      <c r="N164">
+        <v>43250</v>
+      </c>
+      <c r="O164">
+        <v>46500</v>
+      </c>
+      <c r="P164">
+        <v>49760</v>
+      </c>
+      <c r="Q164">
+        <v>53025</v>
+      </c>
+      <c r="R164">
+        <v>56300</v>
       </c>
       <c r="V164" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="W164" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B165" t="s">
         <v>499</v>
       </c>
-      <c r="I165">
-        <v>28900</v>
-      </c>
-      <c r="K165">
-        <v>36500</v>
+      <c r="D165">
+        <v>36800</v>
       </c>
       <c r="V165" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="W165" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B166" t="s">
         <v>499</v>
       </c>
+      <c r="H166">
+        <v>30000</v>
+      </c>
+      <c r="I166">
+        <v>34000</v>
+      </c>
       <c r="J166">
-        <v>36800</v>
+        <v>37100</v>
       </c>
       <c r="K166">
-        <v>41700</v>
+        <v>42100</v>
       </c>
       <c r="L166">
-        <v>46600</v>
+        <v>47100</v>
+      </c>
+      <c r="M166">
+        <v>52200</v>
+      </c>
+      <c r="N166">
+        <v>57200</v>
       </c>
       <c r="V166" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="W166" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="167" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B167" t="s">
         <v>499</v>
       </c>
-      <c r="J167">
-        <v>36800</v>
-      </c>
-      <c r="K167">
-        <v>41700</v>
-      </c>
-      <c r="L167">
-        <v>46600</v>
+      <c r="D167">
+        <v>37100</v>
       </c>
       <c r="V167" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="W167" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="168" spans="1:23" ht="375" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B168" t="s">
         <v>499</v>
       </c>
-      <c r="J168">
-        <v>36800</v>
-      </c>
-      <c r="K168">
-        <v>41700</v>
-      </c>
-      <c r="L168">
-        <v>46600</v>
+      <c r="D168">
+        <v>49900</v>
       </c>
       <c r="V168" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="W168" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="315" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B169" t="s">
         <v>499</v>
       </c>
       <c r="D169">
+        <v>37100</v>
+      </c>
+      <c r="V169" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="W169" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>150</v>
+      </c>
+      <c r="B170" t="s">
+        <v>499</v>
+      </c>
+      <c r="I170">
+        <v>28500</v>
+      </c>
+      <c r="J170">
+        <v>37100</v>
+      </c>
+      <c r="K170">
+        <v>42100</v>
+      </c>
+      <c r="V170" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="W170" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>151</v>
+      </c>
+      <c r="B171" t="s">
+        <v>499</v>
+      </c>
+      <c r="K171">
+        <v>33400</v>
+      </c>
+      <c r="L171">
+        <v>43420</v>
+      </c>
+      <c r="V171" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="W171" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>152</v>
+      </c>
+      <c r="B172" t="s">
+        <v>499</v>
+      </c>
+      <c r="H172">
+        <v>30000</v>
+      </c>
+      <c r="I172">
+        <v>34000</v>
+      </c>
+      <c r="J172">
+        <v>37100</v>
+      </c>
+      <c r="K172">
+        <v>42100</v>
+      </c>
+      <c r="L172">
+        <v>47100</v>
+      </c>
+      <c r="V172" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="W172" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>153</v>
+      </c>
+      <c r="B173" t="s">
+        <v>499</v>
+      </c>
+      <c r="H173">
+        <v>30000</v>
+      </c>
+      <c r="I173">
+        <v>34000</v>
+      </c>
+      <c r="J173">
+        <v>37100</v>
+      </c>
+      <c r="K173">
+        <v>42100</v>
+      </c>
+      <c r="L173">
+        <v>47100</v>
+      </c>
+      <c r="V173" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="W173" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>154</v>
+      </c>
+      <c r="B174" t="s">
+        <v>499</v>
+      </c>
+      <c r="D174">
         <v>57800</v>
       </c>
-      <c r="V169" s="2" t="s">
+      <c r="V174" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="W169" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="170" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="W174" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>155</v>
-      </c>
-      <c r="B170" t="s">
-        <v>204</v>
-      </c>
-      <c r="D170">
-        <v>25850</v>
-      </c>
-      <c r="V170" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="W170" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="171" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>156</v>
-      </c>
-      <c r="B171" t="s">
-        <v>204</v>
-      </c>
-      <c r="D171">
-        <v>25850</v>
-      </c>
-      <c r="V171" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="W171" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="172" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>157</v>
-      </c>
-      <c r="B172" t="s">
-        <v>204</v>
-      </c>
-      <c r="D172">
-        <v>25850</v>
-      </c>
-      <c r="V172" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="W172" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="173" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>158</v>
-      </c>
-      <c r="B173" t="s">
-        <v>204</v>
-      </c>
-      <c r="D173">
-        <v>25850</v>
-      </c>
-      <c r="V173" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="W173" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="174" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>159</v>
-      </c>
-      <c r="B174" t="s">
-        <v>204</v>
-      </c>
-      <c r="D174">
-        <v>25850</v>
-      </c>
-      <c r="V174" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="W174" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="175" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>160</v>
       </c>
       <c r="B175" t="s">
         <v>204</v>
@@ -7437,9 +7677,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B176" t="s">
         <v>204</v>
@@ -7454,9 +7694,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="177" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B177" t="s">
         <v>204</v>
@@ -7471,9 +7711,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B178" t="s">
         <v>204</v>
@@ -7488,500 +7728,611 @@
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B179" t="s">
         <v>204</v>
       </c>
       <c r="D179">
-        <v>12000</v>
-      </c>
-      <c r="T179" t="s">
-        <v>205</v>
+        <v>25850</v>
       </c>
       <c r="V179" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="W179" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B180" t="s">
         <v>204</v>
       </c>
       <c r="D180">
-        <v>12000</v>
-      </c>
-      <c r="T180" t="s">
-        <v>206</v>
+        <v>25850</v>
       </c>
       <c r="V180" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="W180" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="181" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B181" t="s">
         <v>204</v>
       </c>
       <c r="D181">
-        <v>12000</v>
-      </c>
-      <c r="T181" t="s">
-        <v>207</v>
+        <v>25850</v>
       </c>
       <c r="V181" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="W181" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="182" spans="1:23" ht="255" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B182" t="s">
         <v>204</v>
       </c>
       <c r="D182">
+        <v>25850</v>
+      </c>
+      <c r="V182" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="W182" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>163</v>
+      </c>
+      <c r="B183" t="s">
+        <v>204</v>
+      </c>
+      <c r="D183">
+        <v>25850</v>
+      </c>
+      <c r="V183" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="W183" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>164</v>
+      </c>
+      <c r="B184" t="s">
+        <v>204</v>
+      </c>
+      <c r="D184">
         <v>12000</v>
       </c>
-      <c r="T182" t="s">
+      <c r="T184" t="s">
+        <v>205</v>
+      </c>
+      <c r="V184" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="W184" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>165</v>
+      </c>
+      <c r="B185" t="s">
+        <v>204</v>
+      </c>
+      <c r="D185">
+        <v>12000</v>
+      </c>
+      <c r="T185" t="s">
+        <v>206</v>
+      </c>
+      <c r="V185" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="W185" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>166</v>
+      </c>
+      <c r="B186" t="s">
+        <v>204</v>
+      </c>
+      <c r="D186">
+        <v>12000</v>
+      </c>
+      <c r="T186" t="s">
+        <v>207</v>
+      </c>
+      <c r="V186" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="W186" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>167</v>
+      </c>
+      <c r="B187" t="s">
+        <v>204</v>
+      </c>
+      <c r="D187">
+        <v>12000</v>
+      </c>
+      <c r="T187" t="s">
         <v>208</v>
       </c>
-      <c r="V182" s="2" t="s">
+      <c r="V187" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="W182" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="W187" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
         <v>178</v>
-      </c>
-      <c r="B183" t="s">
-        <v>195</v>
-      </c>
-      <c r="C183">
-        <v>18</v>
-      </c>
-      <c r="J183">
-        <v>7800</v>
-      </c>
-      <c r="K183">
-        <v>9600</v>
-      </c>
-      <c r="L183">
-        <v>11400</v>
-      </c>
-      <c r="M183">
-        <v>13200</v>
-      </c>
-      <c r="N183">
-        <v>15100</v>
-      </c>
-      <c r="T183" t="s">
-        <v>241</v>
-      </c>
-      <c r="W183" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>179</v>
-      </c>
-      <c r="B184" t="s">
-        <v>195</v>
-      </c>
-      <c r="C184">
-        <v>24</v>
-      </c>
-      <c r="J184">
-        <v>7800</v>
-      </c>
-      <c r="K184">
-        <v>9600</v>
-      </c>
-      <c r="L184">
-        <v>11400</v>
-      </c>
-      <c r="M184">
-        <v>13200</v>
-      </c>
-      <c r="N184">
-        <v>15100</v>
-      </c>
-      <c r="T184" t="s">
-        <v>226</v>
-      </c>
-      <c r="W184" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>180</v>
-      </c>
-      <c r="B185" t="s">
-        <v>195</v>
-      </c>
-      <c r="C185">
-        <v>27</v>
-      </c>
-      <c r="J185">
-        <v>7800</v>
-      </c>
-      <c r="K185">
-        <v>9600</v>
-      </c>
-      <c r="T185" t="s">
-        <v>234</v>
-      </c>
-      <c r="W185" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>181</v>
-      </c>
-      <c r="B186" t="s">
-        <v>195</v>
-      </c>
-      <c r="C186">
-        <v>21</v>
-      </c>
-      <c r="J186">
-        <v>7800</v>
-      </c>
-      <c r="K186">
-        <v>9600</v>
-      </c>
-      <c r="L186">
-        <v>11400</v>
-      </c>
-      <c r="M186">
-        <v>13200</v>
-      </c>
-      <c r="T186" t="s">
-        <v>231</v>
-      </c>
-      <c r="W186" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>182</v>
-      </c>
-      <c r="B187" t="s">
-        <v>195</v>
-      </c>
-      <c r="C187">
-        <v>22</v>
-      </c>
-      <c r="J187">
-        <v>7800</v>
-      </c>
-      <c r="K187">
-        <v>9600</v>
-      </c>
-      <c r="L187">
-        <v>11400</v>
-      </c>
-      <c r="M187">
-        <v>13200</v>
-      </c>
-      <c r="T187" t="s">
-        <v>249</v>
-      </c>
-      <c r="W187" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>183</v>
       </c>
       <c r="B188" t="s">
         <v>195</v>
       </c>
       <c r="C188">
-        <v>23</v>
-      </c>
-      <c r="D188">
-        <v>10300</v>
+        <v>19</v>
+      </c>
+      <c r="J188">
+        <v>7800</v>
+      </c>
+      <c r="K188">
+        <v>9600</v>
+      </c>
+      <c r="L188">
+        <v>11400</v>
+      </c>
+      <c r="M188">
+        <v>13200</v>
+      </c>
+      <c r="N188">
+        <v>15100</v>
       </c>
       <c r="T188" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="W188" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>184</v>
+        <v>502</v>
       </c>
       <c r="B189" t="s">
         <v>195</v>
       </c>
       <c r="C189">
-        <v>19</v>
-      </c>
-      <c r="D189">
-        <v>10300</v>
-      </c>
-      <c r="T189" t="s">
-        <v>245</v>
-      </c>
-      <c r="W189" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="J189">
+        <v>7800</v>
+      </c>
+      <c r="K189">
+        <v>9600</v>
+      </c>
+      <c r="L189">
+        <v>11400</v>
+      </c>
+      <c r="M189">
+        <v>13200</v>
+      </c>
+      <c r="N189">
+        <v>15100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B190" t="s">
         <v>195</v>
       </c>
       <c r="C190">
-        <v>25</v>
-      </c>
-      <c r="D190">
-        <v>11450</v>
+        <v>24</v>
+      </c>
+      <c r="J190">
+        <v>7800</v>
+      </c>
+      <c r="K190">
+        <v>9600</v>
+      </c>
+      <c r="L190">
+        <v>11400</v>
+      </c>
+      <c r="M190">
+        <v>13200</v>
+      </c>
+      <c r="N190">
+        <v>15100</v>
       </c>
       <c r="T190" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="W190" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B191" t="s">
         <v>195</v>
       </c>
       <c r="C191">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J191">
-        <v>10300</v>
+        <v>7800</v>
       </c>
       <c r="K191">
-        <v>12700</v>
-      </c>
-      <c r="M191">
-        <v>17600</v>
+        <v>9600</v>
       </c>
       <c r="T191" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="W191" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B192" t="s">
         <v>195</v>
       </c>
       <c r="C192">
-        <v>20</v>
-      </c>
-      <c r="D192">
-        <v>10300</v>
+        <v>21</v>
+      </c>
+      <c r="J192">
+        <v>7800</v>
+      </c>
+      <c r="K192">
+        <v>9600</v>
+      </c>
+      <c r="L192">
+        <v>11400</v>
+      </c>
+      <c r="M192">
+        <v>13200</v>
       </c>
       <c r="T192" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="W192" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B193" t="s">
         <v>195</v>
       </c>
       <c r="C193">
-        <v>28</v>
-      </c>
-      <c r="D193">
+        <v>22</v>
+      </c>
+      <c r="J193">
         <v>7800</v>
       </c>
+      <c r="K193">
+        <v>9600</v>
+      </c>
+      <c r="L193">
+        <v>11400</v>
+      </c>
+      <c r="M193">
+        <v>13200</v>
+      </c>
       <c r="T193" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="W193" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B194" t="s">
         <v>195</v>
       </c>
       <c r="C194">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D194">
-        <v>7800</v>
+        <v>10300</v>
       </c>
       <c r="T194" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="W194" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B195" t="s">
         <v>195</v>
       </c>
       <c r="C195">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D195">
-        <v>7800</v>
+        <v>10300</v>
       </c>
       <c r="T195" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="W195" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B196" t="s">
         <v>195</v>
       </c>
       <c r="C196">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D196">
-        <v>10300</v>
+        <v>11450</v>
       </c>
       <c r="T196" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="W196" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B197" t="s">
         <v>195</v>
       </c>
       <c r="C197">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J197">
-        <v>7800</v>
+        <v>10300</v>
       </c>
       <c r="K197">
-        <v>9600</v>
-      </c>
-      <c r="L197">
-        <v>11400</v>
+        <v>12700</v>
       </c>
       <c r="M197">
-        <v>13200</v>
+        <v>17600</v>
       </c>
       <c r="T197" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="W197" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B198" t="s">
         <v>195</v>
       </c>
       <c r="C198">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D198">
-        <v>10825</v>
+        <v>10300</v>
       </c>
       <c r="T198" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="W198" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B199" t="s">
         <v>195</v>
       </c>
       <c r="C199">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D199">
-        <v>18000</v>
+        <v>7800</v>
       </c>
       <c r="T199" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="W199" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="B200" t="s">
         <v>195</v>
       </c>
       <c r="C200">
+        <v>29</v>
+      </c>
+      <c r="D200">
+        <v>7800</v>
+      </c>
+      <c r="T200" t="s">
+        <v>227</v>
+      </c>
+      <c r="W200" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>190</v>
+      </c>
+      <c r="B201" t="s">
+        <v>195</v>
+      </c>
+      <c r="C201">
+        <v>34</v>
+      </c>
+      <c r="D201">
+        <v>7800</v>
+      </c>
+      <c r="T201" t="s">
+        <v>228</v>
+      </c>
+      <c r="W201" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>191</v>
+      </c>
+      <c r="B202" t="s">
+        <v>195</v>
+      </c>
+      <c r="C202">
+        <v>31</v>
+      </c>
+      <c r="D202">
+        <v>10300</v>
+      </c>
+      <c r="T202" t="s">
+        <v>256</v>
+      </c>
+      <c r="W202" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>192</v>
+      </c>
+      <c r="B203" t="s">
+        <v>195</v>
+      </c>
+      <c r="C203">
+        <v>32</v>
+      </c>
+      <c r="J203">
+        <v>7800</v>
+      </c>
+      <c r="K203">
+        <v>9600</v>
+      </c>
+      <c r="L203">
+        <v>11400</v>
+      </c>
+      <c r="M203">
+        <v>13200</v>
+      </c>
+      <c r="T203" t="s">
+        <v>258</v>
+      </c>
+      <c r="W203" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>193</v>
+      </c>
+      <c r="B204" t="s">
+        <v>195</v>
+      </c>
+      <c r="C204">
+        <v>33</v>
+      </c>
+      <c r="D204">
+        <v>10825</v>
+      </c>
+      <c r="T204" t="s">
+        <v>237</v>
+      </c>
+      <c r="W204" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>194</v>
+      </c>
+      <c r="B205" t="s">
+        <v>195</v>
+      </c>
+      <c r="C205">
+        <v>35</v>
+      </c>
+      <c r="D205">
+        <v>18000</v>
+      </c>
+      <c r="T205" t="s">
+        <v>259</v>
+      </c>
+      <c r="W205" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>246</v>
+      </c>
+      <c r="B206" t="s">
+        <v>195</v>
+      </c>
+      <c r="C206">
         <v>30</v>
       </c>
-      <c r="D200">
+      <c r="D206">
         <v>10300</v>
       </c>
-      <c r="T200" t="s">
+      <c r="T206" t="s">
         <v>247</v>
       </c>
     </row>
